--- a/AI Audit Log_Luong_Dang_Hoang_Luu.xlsx
+++ b/AI Audit Log_Luong_Dang_Hoang_Luu.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HoangLuu\Desktop\SWD392\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HoangLuu\Documents\GitHub\ai-audit-log-HoangLuu217\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70DCB39-EB21-4420-8E6B-D11EF6DDF76C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73BB380-4601-447D-805E-B2C2935F09F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="142">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -421,19 +419,134 @@
   <si>
     <t>AI trả về: UC đặt lịch map sang AppointmentDTO, AppointmentRepository,
  AppointmentService, AppointmentController, PatientAppointmentBooking; UC thanh toán phụ thuộc PayOS; UC chatbot phụ thuộc Gemini; UC email/OTP phụ thuộc SMTP; UC chat phụ thuộc WebSocket. Quyết định người học: Dùng bảng mapping này để bảo đảm thiết kế dữ liệu tuần 2 không tách rời luồng sử dụng thật.</t>
+  </si>
+  <si>
+    <t>Thành phần cấu trúc</t>
+  </si>
+  <si>
+    <t>Tiêu chí so sánh chi tiết</t>
+  </si>
+  <si>
+    <t>Giải pháp của AI (Thiết kế mẫu)</t>
+  </si>
+  <si>
+    <t>Đánh giá chuyên môn &amp; Hướng tối ưu bài thi</t>
+  </si>
+  <si>
+    <t>Question 1 (Class Diagram)</t>
+  </si>
+  <si>
+    <t>Mô hình hóa lớp thực thể (Domain Entities Model)</t>
+  </si>
+  <si>
+    <t>Rich Domain Model (Mô hình phong phú): Đưa các hàm logic nghiệp vụ cốt lõi vào thẳng các Entity (ví dụ: Car có checkAvailability(), Booking có calculateTotal(), confirmBooking()).</t>
+  </si>
+  <si>
+    <t>Anemic Domain Model (Mô hình nghèo nàn): Chỉ khai báo các thuộc tính dữ liệu thô (Attributes) cho Entity. Toàn bộ các hàm xử lý logic kiểm tra và tính toán đều bị dồn đẩy hết lên tầng Service.</t>
+  </si>
+  <si>
+    <t>Bài của bạn xuất sắc hơn. Việc phân bổ hành vi về đúng đối tượng sở hữu dữ liệu thể hiện tư duy lập trình hướng đối tượng (OOP) rất sâu sắc và thực tế.</t>
+  </si>
+  <si>
+    <t>Tổ chức thiết kế tầng nghiệp vụ (Service Layer)</t>
+  </si>
+  <si>
+    <t>Phân rã đơn nhiệm (SRP): Tách biệt hệ thống thành 2 Service riêng biệt là BookingService và PaymentService. Tuy nhiên, PaymentService đang đứng cô lập, thiếu quan hệ Dependency (mũi tên đứt nét) hướng tới PaymentRepository.</t>
+  </si>
+  <si>
+    <t>Tập trung hóa (Centralized): Gộp chung hoặc chỉ minh họa một lớp PaymentService đại diện để làm mẫu. AI vẽ đầy đủ tất cả các đường mũi tên Dependency hướng từ Service xuống các Repository bên dưới.</t>
+  </si>
+  <si>
+    <t>Bài của bạn tổ chức tốt hơn nhưng thiếu nét vẽ. Bạn cần bổ sung mũi tên nét đứt (--&gt;) từ PaymentService trỏ đến PaymentRepository ở Câu 1 để hợp thức hóa cấu trúc phân tầng.</t>
+  </si>
+  <si>
+    <t>Hiện thực hóa mẫu thiết kế (Repository Pattern)</t>
+  </si>
+  <si>
+    <t>Khai báo tường minh: Định nghĩa chính xác Interface IGenericRepository&lt;T&gt; và chỉ rõ kiểu tham số hóa cụ thể (Ví dụ: BookingRepository implements IGenericRepository&lt;Booking&gt;).</t>
+  </si>
+  <si>
+    <t>Khai báo khái quát: Chỉ sử dụng ký hiệu ngắn gọn CarRepository implements IRepository mà không ghi rõ kiểu nhận vào &lt;T&gt; của Generic trên sơ đồ.</t>
+  </si>
+  <si>
+    <t>Bài của bạn chuẩn quy ước thiết kế hơn. Việc chỉ định rõ ràng &lt;Booking&gt;, &lt;Payment&gt;, &lt;Car&gt; giúp sơ đồ đạt mức Design-level hoàn hảo, tường minh về mặt mã nguồn tương lai.</t>
+  </si>
+  <si>
+    <t>Question 2 (Sequence Diagram)</t>
+  </si>
+  <si>
+    <t>Tính nhất quán giữa các sơ đồ (Architectural Consistency)</t>
+  </si>
+  <si>
+    <t>Luồng chi tiết - Bị lệch kiến trúc: Sơ đồ tuần tự xử lý rất sâu khi cho BookingService gọi sang PaymentService qua hàm payDeposit(). Nhưng ở Sơ đồ lớp (Câu 1), hai Service này đang đứng độc lập, không hề nối với nhau bằng bất kỳ quan hệ nào.</t>
+  </si>
+  <si>
+    <t>Luồng tối giản - Đồng bộ kiến trúc: Để đảm bảo an toàn tuyệt đối trong thời gian thi, AI chỉ cho Controller gọi duy nhất một Service xử lý xuyên suốt, tránh việc các Service gọi chéo nhau làm phát sinh các mối quan hệ phức tạp.</t>
+  </si>
+  <si>
+    <t>Lỗi cần sửa gấp. Bạn hãy giữ nguyên luồng Sequence rất hay của bạn. Nhưng ở Sơ đồ lớp (Câu 1), bạn bắt buộc phải vẽ thêm một mũi tên đứt nét Dependency trỏ từ BookingService sang PaymentService.</t>
+  </si>
+  <si>
+    <t>Quản lý vòng đời và lưu trữ dữ liệu (Save/Update Object)</t>
+  </si>
+  <si>
+    <t>Kiểm soát trạng thái chặt chẽ: Thể hiện rõ ràng quy trình tuần tự: Service gọi Entity để cập nhật trạng thái trước (setStatus), sau đó mới gọi Repository tương ứng để lưu xuống database (update(booking)).</t>
+  </si>
+  <si>
+    <t>Tóm tắt quy trình: Gộp hành động lại, chỉ gọi thẳng hàm save(booking) hoặc update(car) từ Repository nhằm tối giản hóa các bước hiển thị trên sơ đồ tuần tự.</t>
+  </si>
+  <si>
+    <t>Bài của bạn rất logic. Việc tách biệt bước thay đổi trạng thái trên Object trong bộ nhớ và bước đồng bộ dữ liệu xuống Database qua Repository là hoàn toàn chính xác với thực tế.</t>
+  </si>
+  <si>
+    <t>Question 3 (Activity Diagram)</t>
+  </si>
+  <si>
+    <t>Phân chia làn bơi theo cấp độ thiết kế (Swimlanes - Level 2)</t>
+  </si>
+  <si>
+    <t>Tập trung luồng nghiệp vụ (Level 1): Bạn chỉ chia làm 2 làn bơi là Staff (Con người) và System (Hệ thống chung). Việc gộp cả giao diện hiển thị lẫn logic xử lý ngầm vào một làn System làm sơ đồ chưa đạt độ chi tiết "Design".</t>
+  </si>
+  <si>
+    <t>Tách biệt kiến trúc thành phần (Level 2): Phân rã rõ ràng thành 3 làn bơi tách biệt: Staff (Actor) -&gt; UI / Controller (Thành phần giao diện tiếp nhận) -&gt; Backend Service (Thành phần xử lý logic ngầm).</t>
+  </si>
+  <si>
+    <t>Điểm trừ đáng tiếc của bạn. Đề bài yêu cầu rất rõ mức Level 2 – Design (Swimlanes đại diện cho Actor và Component/Service). Bạn nên kẻ thêm một đường dọc để chia làn System thành 2 làn nhỏ: System UI và Backend Service.</t>
+  </si>
+  <si>
+    <t>Kỹ thuật sử dụng các nút điều hướng (UML Notations)</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa đồ họa: Sử dụng rất chính xác các nút rẽ nhánh điều kiện (Decision Diamond), nút gộp luồng (Merge Node) hình thoi, nút bắt đầu và nút kết thúc đúng quy ước quốc tế.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa đồ họa: Sử dụng cấu trúc hình thoi rẽ nhánh điều kiện tương tự để kiểm tra hư hại và tính toán chi phí phạt phát sinh.</t>
+  </si>
+  <si>
+    <t>Cả hai bên đều làm rất tốt. Luồng đi mạch lạc, có điểm bắt đầu và kết thúc rõ ràng, không bị lỗi mũi tên cụt hay lặp vô hạn.</t>
+  </si>
+  <si>
+    <t>Giải pháp của Bạn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -467,8 +580,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,8 +620,26 @@
         <fgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -544,14 +692,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -565,23 +729,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="3" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{990CB1A6-12C2-4497-97CE-874DFE4B5686}"/>
     <cellStyle name="Note" xfId="3" builtinId="10"/>
     <cellStyle name="Output" xfId="2" builtinId="21"/>
   </cellStyles>
@@ -1480,9 +1666,177 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" customWidth="1"/>
+    <col min="6" max="6" width="88.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="182.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="146.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="144" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="167.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI Audit Log_Luong_Dang_Hoang_Luu.xlsx
+++ b/AI Audit Log_Luong_Dang_Hoang_Luu.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HoangLuu\Documents\GitHub\ai-audit-log-HoangLuu217\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A73BB380-4601-447D-805E-B2C2935F09F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05D62DB-1E93-4016-ABD5-507B182BE5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week1" sheetId="2" r:id="rId2"/>
     <sheet name="Week2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Week3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId5"/>
+    <sheet name="Week6" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="204">
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -527,13 +529,224 @@
   </si>
   <si>
     <t>Giải pháp của Bạn</t>
+  </si>
+  <si>
+    <t>Mô hình hóa thực thể nghiệp vụ (Domain Model)</t>
+  </si>
+  <si>
+    <t>Xây dựng đầy đủ User, Customer, Staff, Chef theo quan hệ kế thừa. Order chứa OrderItem, Payment liên kết 1-1 với Order.</t>
+  </si>
+  <si>
+    <t>Thiết kế tương tự nhưng bổ sung rõ stereotype Entity và chuẩn hóa naming convention UML.</t>
+  </si>
+  <si>
+    <t>Bài của bạn đáp ứng đầy đủ yêu cầu đề. Nên bổ sung stereotype &lt;&gt; để tăng tính Design-Level và chuyên nghiệp.</t>
+  </si>
+  <si>
+    <t>Áp dụng Repository Pattern</t>
+  </si>
+  <si>
+    <t>Khai báo Generic Repository và các Repository chuyên biệt như OrderRepository, PaymentRepository.</t>
+  </si>
+  <si>
+    <t>Tương tự nhưng thể hiện rõ quan hệ Realization (..</t>
+  </si>
+  <si>
+    <t>&gt;) từ Repository tới IRepository.</t>
+  </si>
+  <si>
+    <t>Thiết kế Service Layer</t>
+  </si>
+  <si>
+    <t>Tách OrderService và PaymentService theo nguyên tắc Single Responsibility Principle (SRP).</t>
+  </si>
+  <si>
+    <t>AI thường vẽ đầy đủ Dependency giữa các Service và Repository tương ứng.</t>
+  </si>
+  <si>
+    <t>Nếu PaymentService chưa nối tới PaymentRepository thì cần bổ sung Dependency nét đứt để hoàn chỉnh kiến trúc phân tầng.</t>
+  </si>
+  <si>
+    <t>Sử dụng UML Relationship</t>
+  </si>
+  <si>
+    <t>Kết hợp Inheritance, Composition, Association và Dependency.</t>
+  </si>
+  <si>
+    <t>AI tối ưu thêm Multiplicity và Direction Navigation cho từng quan hệ.</t>
+  </si>
+  <si>
+    <t>Đảm bảo Order ♦── OrderItem là Composition, Menu ◇── MenuItem là Aggregation để đúng ngữ nghĩa UML.</t>
+  </si>
+  <si>
+    <t>Tuân thủ Layered Architecture</t>
+  </si>
+  <si>
+    <t>Luồng đi qua UI → Controller → Service → Repository → Entity.</t>
+  </si>
+  <si>
+    <t>Thiết kế mẫu giữ nguyên luồng phân tầng và hạn chế gọi chéo giữa Service.</t>
+  </si>
+  <si>
+    <t>Đây là cấu trúc chuẩn đề bài yêu cầu. Không nên cho UI truy cập Repository trực tiếp vì vi phạm Layered Architecture.</t>
+  </si>
+  <si>
+    <t>Sử dụng Repository Pattern trong Sequence</t>
+  </si>
+  <si>
+    <t>Service gọi save(), update(), findById() thông qua Repository.</t>
+  </si>
+  <si>
+    <t>AI luôn thể hiện rõ Repository Method Calls.</t>
+  </si>
+  <si>
+    <t>Bài thi bắt buộc phải có lời gọi Repository để chứng minh Repository Pattern đã được áp dụng thực tế.</t>
+  </si>
+  <si>
+    <t>Xử lý thanh toán thành công/thất bại</t>
+  </si>
+  <si>
+    <t>Dùng khối alt Payment Success và Payment Failure.</t>
+  </si>
+  <si>
+    <t>Tương tự nhưng thường thêm bước cập nhật trạng thái Order.</t>
+  </si>
+  <si>
+    <t>Đây là yêu cầu trọng tâm của đề. Thiếu alt fragment thường bị trừ điểm đáng kể.</t>
+  </si>
+  <si>
+    <t>Quản lý trạng thái đối tượng</t>
+  </si>
+  <si>
+    <t>Service cập nhật Order Status trước khi lưu Repository.</t>
+  </si>
+  <si>
+    <t>Một số thiết kế mẫu gộp thẳng vào save(order).</t>
+  </si>
+  <si>
+    <t>Cách của bạn tốt hơn vì phản ánh đúng vòng đời Object trong bộ nhớ và Database.</t>
+  </si>
+  <si>
+    <t>Question 3 (State Diagram)</t>
+  </si>
+  <si>
+    <t>Thiết kế vòng đời Order</t>
+  </si>
+  <si>
+    <t>Bao gồm Created → Confirmed → Paid → Preparing → ReadyToServe → Served → Completed.</t>
+  </si>
+  <si>
+    <t>Tương tự theo đề bài.</t>
+  </si>
+  <si>
+    <t>Đây là luồng nghiệp vụ chính bắt buộc phải có. Thiếu bất kỳ trạng thái nào đều làm giảm tính đầy đủ của mô hình.</t>
+  </si>
+  <si>
+    <t>Xử lý Payment Failure</t>
+  </si>
+  <si>
+    <t>Tạo trạng thái PaymentFailed và Cancelled riêng biệt.</t>
+  </si>
+  <si>
+    <t>AI thường bổ sung Choice Point và Guard Conditions chuẩn UML State Machine.</t>
+  </si>
+  <si>
+    <t>Phiên bản có Choice Point đạt chuẩn UML quốc tế hơn cách nối trực tiếp paySuccess/payFail.</t>
+  </si>
+  <si>
+    <t>Sử dụng Choice Pseudostate</t>
+  </si>
+  <si>
+    <t>Confirmed → pay_choice : payOrder, sau đó rẽ nhánh bằng Guard Conditions.</t>
+  </si>
+  <si>
+    <t>Thiết kế mẫu sử dụng state pay_choice &lt;&gt;.</t>
+  </si>
+  <si>
+    <t>Đây là cách mô hình hóa chuyên nghiệp và thường được giảng viên đánh giá cao ở mức Design-Level UML.</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa Guard Conditions</t>
+  </si>
+  <si>
+    <t>[payment_successful], [payment_failed], [system_auto_cancel].</t>
+  </si>
+  <si>
+    <t>AI áp dụng đầy đủ UML Guard Syntax.</t>
+  </si>
+  <si>
+    <t>Không nên dùng paySuccess/payFail như Event độc lập sau bước thanh toán vì không đúng bản chất Decision Node.</t>
+  </si>
+  <si>
+    <t>Quản lý kết thúc luồng</t>
+  </si>
+  <si>
+    <r>
+      <t>Completed → [</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] và Cancelled → [</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>].</t>
+    </r>
+  </si>
+  <si>
+    <t>Tương tự.</t>
+  </si>
+  <si>
+    <t>Đúng chuẩn UML khi tất cả trạng thái kết thúc đều dẫn về Final State.</t>
+  </si>
+  <si>
+    <t>Tổng thể bài thi</t>
+  </si>
+  <si>
+    <t>Tính nhất quán kiến trúc (Architectural Consistency)</t>
+  </si>
+  <si>
+    <t>Layered Architecture được áp dụng xuyên suốt Class Diagram, Sequence Diagram và State Diagram.</t>
+  </si>
+  <si>
+    <t>AI luôn kiểm tra sự đồng bộ giữa các sơ đồ.</t>
+  </si>
+  <si>
+    <t>Đây là tiêu chí giảng viên thường kiểm tra đầu tiên. Nếu Service gọi nhau trong Sequence thì Class Diagram phải phản ánh Dependency tương ứng.</t>
+  </si>
+  <si>
+    <t>Mức độ đạt Design-Level UML</t>
+  </si>
+  <si>
+    <t>Có đầy đủ Domain, Service, Repository, State Machine và Sequence Flow.</t>
+  </si>
+  <si>
+    <t>AI bổ sung thêm UML notation chuẩn hóa quốc tế.</t>
+  </si>
+  <si>
+    <t>Muốn đạt điểm tối đa, nên bổ sung stereotype (&lt;&gt;, &lt;&gt;, &lt;&gt;, &lt;&gt;) và Choice Point trong State Diagram.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -597,8 +810,26 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -636,6 +867,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F5F9"/>
         <bgColor rgb="FFF2F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -715,7 +952,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -762,6 +999,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1839,4 +2082,350 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C601FC6-3535-4F61-8A1F-3647AF29445A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E358DF2-5DF0-438C-A8EC-05A3DDADB5F4}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="32.140625" customWidth="1"/>
+    <col min="3" max="3" width="46.42578125" customWidth="1"/>
+    <col min="4" max="4" width="107.42578125" customWidth="1"/>
+    <col min="5" max="5" width="84.140625" customWidth="1"/>
+    <col min="6" max="6" width="98.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>6</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>7</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>8</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>